--- a/data/jjj/wind.xlsx
+++ b/data/jjj/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,145 +439,277 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46145.79166666666</v>
+        <v>46279.41666666666</v>
       </c>
       <c r="B2" t="n">
-        <v>71.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46145.83333333334</v>
+        <v>46279.45833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>50.99999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46145.875</v>
+        <v>46279.5</v>
       </c>
       <c r="B4" t="n">
-        <v>133.3</v>
+        <v>92.99999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46145.91666666666</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="B5" t="n">
-        <v>188.7</v>
+        <v>91.30000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46145.95833333334</v>
+        <v>46279.58333333334</v>
       </c>
       <c r="B6" t="n">
-        <v>218.7</v>
+        <v>112.2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46146</v>
+        <v>46279.625</v>
       </c>
       <c r="B7" t="n">
-        <v>229.9</v>
+        <v>129.4</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46146.04166666666</v>
+        <v>46279.66666666666</v>
       </c>
       <c r="B8" t="n">
-        <v>250.1</v>
+        <v>112.5</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46146.08333333334</v>
+        <v>46279.70833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>308.6</v>
+        <v>112.1</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46146.125</v>
+        <v>46279.75</v>
       </c>
       <c r="B10" t="n">
-        <v>307.1</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46146.16666666666</v>
+        <v>46279.79166666666</v>
       </c>
       <c r="B11" t="n">
-        <v>307.7</v>
+        <v>76.5</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46146.20833333334</v>
+        <v>46279.83333333334</v>
       </c>
       <c r="B12" t="n">
-        <v>306.7</v>
+        <v>35.9</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46146.25</v>
+        <v>46279.875</v>
       </c>
       <c r="B13" t="n">
-        <v>305.1999999999999</v>
+        <v>33.8</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46146.29166666666</v>
+        <v>46279.91666666666</v>
       </c>
       <c r="B14" t="n">
-        <v>303.9999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46279.95833333334</v>
+      </c>
+      <c r="B15" t="n">
+        <v>54.20000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46280.04166666666</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91.30000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46280.125</v>
+      </c>
+      <c r="B19" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46280.16666666666</v>
+      </c>
+      <c r="B20" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46280.20833333334</v>
+      </c>
+      <c r="B21" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46280.25</v>
+      </c>
+      <c r="B22" t="n">
+        <v>86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46280.29166666666</v>
+      </c>
+      <c r="B23" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46280.33333333334</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46280.375</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46280.41666666666</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
